--- a/AAII_Financials/Quarterly/PG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="92">
   <si>
     <t>PG</t>
   </si>
@@ -656,515 +656,527 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>21204000</v>
+      </c>
+      <c r="E8" s="3">
         <v>21235000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>22208000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>22386000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>20889000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>19776000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>21882000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>21737000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>20532000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>20195000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>21441000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>21871000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>20553000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>20068000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>20773000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>20612000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>19515000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>19381000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>20953000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>20338000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>18946000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>18109000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>19745000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>19318000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>17698000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>17214000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>18240000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>17798000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>17094000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>16462000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>17438000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>16690000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>16503000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>16281000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>17395000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>16653000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>16079000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>15605000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>16856000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>16518000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>10732000</v>
+      </c>
+      <c r="E9" s="3">
         <v>10584000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>10654000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>10787000</v>
       </c>
-      <c r="G9" s="3">
-        <v>10572000</v>
-      </c>
       <c r="H9" s="3">
+        <v>10481000</v>
+      </c>
+      <c r="I9" s="3">
         <v>9694000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>10418000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>10421000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>10100000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>9855000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>10144000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>10501000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>10453000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>10404000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>10897000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>10846000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>10802000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>10326000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>10664000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>10365000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>9791000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>8922000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>9253000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>9142000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>8659000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>8518000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>8806000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>8653000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>8410000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>8342000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>8776000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>8420000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>17634000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>8213000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>17270000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>16380000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>8115000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>7704000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>8150000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>7973000</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>10472000</v>
+      </c>
+      <c r="E10" s="3">
         <v>10651000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>11554000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>11599000</v>
       </c>
-      <c r="G10" s="3">
-        <v>10317000</v>
-      </c>
       <c r="H10" s="3">
+        <v>10408000</v>
+      </c>
+      <c r="I10" s="3">
         <v>10082000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>11464000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>11316000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>10432000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>10340000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>11297000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>11370000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>10100000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>9664000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>9876000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>9766000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>8713000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>9055000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>10289000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>9973000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>9155000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>9187000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>10492000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>10176000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>9039000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>8696000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>9434000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>9145000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>8684000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>8120000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>8662000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>8270000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>-1131000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>8068000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>125000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>273000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>7964000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>7901000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>8706000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>8545000</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1207,13 +1219,14 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
+      <c r="D12" s="3">
+        <v>2100000</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>8</v>
@@ -1221,11 +1234,11 @@
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="3">
         <v>2100000</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>8</v>
@@ -1233,11 +1246,11 @@
       <c r="J12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="3">
         <v>2000000</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>8</v>
@@ -1245,11 +1258,11 @@
       <c r="N12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O12" s="3">
+      <c r="O12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P12" s="3">
         <v>2000000</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>8</v>
@@ -1329,8 +1342,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1451,25 +1467,28 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>474000</v>
+      </c>
+      <c r="E14" s="3">
         <v>197000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>369000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>215000</v>
       </c>
-      <c r="G14" s="3">
-        <v>132000</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
+      <c r="H14" s="3">
+        <v>1119000</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
@@ -1477,23 +1496,23 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3">
         <v>665000</v>
       </c>
-      <c r="L14" s="3" t="s">
+      <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1341000</v>
       </c>
-      <c r="N14" s="3" t="s">
+      <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>338000</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>8</v>
@@ -1504,20 +1523,20 @@
       <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3" t="s">
+      <c r="T14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3" t="s">
+      <c r="W14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="X14" s="3">
+        <v>0</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>8</v>
@@ -1525,101 +1544,104 @@
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB14" s="3">
         <v>362000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>222000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>105000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>93000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>8985000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>116000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>177000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>-218000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>554000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>205000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>154000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>157000</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>249000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>157000</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>175000</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>150000</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>812000</v>
+      </c>
+      <c r="E15" s="3">
         <v>785000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>802000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>761000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>723000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>690000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>706000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>728000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>761000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>712000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>721000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>702000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>706000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>692000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1695,8 +1717,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1736,252 +1761,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>16521000</v>
+      </c>
+      <c r="E17" s="3">
         <v>16341000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>16368000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>16212000</v>
       </c>
-      <c r="G17" s="3">
-        <v>15636000</v>
-      </c>
       <c r="H17" s="3">
+        <v>15827000</v>
+      </c>
+      <c r="I17" s="3">
         <v>15067000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>15987000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>15797000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>15585000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>15735000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>15562000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>16006000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>15731000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>15734000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>15988000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>15673000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>15917000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>15357000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>15785000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>15315000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>15406000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>14324000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>14365000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>14037000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>14221000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>13764000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>13763000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>13509000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>22287000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>13235000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>13551000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>12782000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>13916000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>12985000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>13476000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>13005000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>13130000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>12245000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>12981000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>12747000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4683000</v>
+      </c>
+      <c r="E18" s="3">
         <v>4894000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>5840000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>6174000</v>
       </c>
-      <c r="G18" s="3">
-        <v>5253000</v>
-      </c>
       <c r="H18" s="3">
+        <v>5062000</v>
+      </c>
+      <c r="I18" s="3">
         <v>4709000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>5895000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>5940000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>4947000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>4460000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>5879000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>5865000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>4822000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>4334000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>4785000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>4939000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3598000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>4024000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>5168000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>5023000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>3540000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>3785000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>5380000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>5281000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>3477000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>3450000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>4477000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>4289000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-5193000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>3227000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>3887000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>3908000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>2587000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>3296000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>3919000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>3648000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>2949000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>3360000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>3875000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>3771000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2024,618 +2056,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>147000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-415000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-55000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-164000</v>
       </c>
-      <c r="G20" s="3">
-        <v>492000</v>
-      </c>
       <c r="H20" s="3">
+        <v>-686000</v>
+      </c>
+      <c r="I20" s="3">
         <v>-57000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-72000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>698000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>299000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-262000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-73000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-34000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>127000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-93000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>221000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>181000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>167000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>156000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>177000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>121000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>141000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>198000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-360000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>152000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>141000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>148000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>155000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>162000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>239000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>182000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>167000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>161000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-26000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>90000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>358000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>218000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>94000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>72000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-497000</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>98000</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>5348000</v>
+      </c>
+      <c r="E21" s="3">
         <v>6094000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>6697000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>7099000</v>
       </c>
-      <c r="G21" s="3">
-        <v>5484000</v>
-      </c>
       <c r="H21" s="3">
+        <v>6471000</v>
+      </c>
+      <c r="I21" s="3">
         <v>5456000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>6673000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>5970000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>5409000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>5434000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>6673000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>6601000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>5401000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>5119000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>5659000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>5783000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>4487000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>4870000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>6029000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>5855000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>4391000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>4666000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>5691000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>6104000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>4432000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>4397000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>5309000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>5174000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-4134000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>4120000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>4704000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>4712000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>3311000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>4102000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>4953000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>4558000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>3763000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>4097000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>4085000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>4597000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>236000</v>
+      </c>
+      <c r="E22" s="3">
         <v>223000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>220000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>197000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>212000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>217000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>240000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>238000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>220000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>233000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>248000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>225000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>240000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>222000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>171000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>123000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>115000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>109000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>106000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>109000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>117000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>106000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>143000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>136000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>157000</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>100000</v>
       </c>
       <c r="AC22" s="3">
         <v>100000</v>
       </c>
       <c r="AD22" s="3">
+        <v>100000</v>
+      </c>
+      <c r="AE22" s="3">
         <v>108000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>111000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>131000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>138000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>129000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>272000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>133000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>244000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>115000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>116000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>96000</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>122000</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>131000</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3934000</v>
+      </c>
+      <c r="E23" s="3">
         <v>4989000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>5421000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>6034000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>4521000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>4660000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>5846000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>5139000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3870000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>4593000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>4496000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>5802000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>4233000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>4288000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>4835000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>4997000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3650000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>4071000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>5239000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>5035000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>3564000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>3877000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>4877000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>5297000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>3461000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>3498000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>4532000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>4343000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-5065000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>3278000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>3916000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>3940000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>2289000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>3253000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>4033000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>3751000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>2927000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>3336000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>3256000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>3738000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>852000</v>
+      </c>
+      <c r="E24" s="3">
         <v>1039000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1090000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1253000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>895000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>868000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1187000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1152000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>726000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>812000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1003000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1246000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>841000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>864000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>876000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1034000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>592000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>704000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>997000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>909000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>656000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>628000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>990000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>989000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>675000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>541000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>789000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>726000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>172000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>502000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>700000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>729000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>499000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>613000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>872000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>881000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>725000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>780000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>695000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>863000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2756,252 +2804,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3082000</v>
+      </c>
+      <c r="E26" s="3">
         <v>3950000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4331000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>4781000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3626000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3792000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4659000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3987000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3144000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3781000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3493000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4556000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>3392000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3424000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3959000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>3963000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>3058000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>3367000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>4242000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>4126000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2908000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>3249000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>3887000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>4308000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2786000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2957000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>3743000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>3617000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-5237000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>2776000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>3216000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>3211000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1790000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>2640000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>3161000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>2870000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>2202000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>2556000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>2561000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>2875000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2970000</v>
+      </c>
+      <c r="E27" s="3">
         <v>3860000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>4246000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>4677000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3539000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3698000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4558000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3887000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3062000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3685000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3398000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4451000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>3312000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3328000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3863000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>3868000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2979000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>3287000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>4153000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>4042000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2832000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>3204000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>3788000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>4211000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>2730000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>2853000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>3653000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>3528000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-5309000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>2681000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>3129000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>3133000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1724000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>2537000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>3033000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>2791000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>2152000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>2462000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>2479000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>2769000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3122,8 +3179,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3202,17 +3262,17 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF29" s="3" t="s">
+      <c r="AE29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AF29" s="3">
+        <v>0</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
@@ -3220,18 +3280,18 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>100000</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>-100000</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>-600000</v>
       </c>
-      <c r="AL29" s="3">
-        <v>0</v>
-      </c>
       <c r="AM29" s="3">
         <v>0</v>
       </c>
@@ -3239,13 +3299,16 @@
         <v>0</v>
       </c>
       <c r="AO29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP29" s="3">
         <v>5335000</v>
       </c>
-      <c r="AP29" s="3">
+      <c r="AQ29" s="3">
         <v>-118000</v>
       </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3366,8 +3429,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3488,252 +3554,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-147000</v>
+      </c>
+      <c r="E32" s="3">
         <v>415000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>55000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>164000</v>
       </c>
-      <c r="G32" s="3">
-        <v>-492000</v>
-      </c>
       <c r="H32" s="3">
+        <v>686000</v>
+      </c>
+      <c r="I32" s="3">
         <v>57000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>72000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-698000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-299000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>262000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>73000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>34000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-127000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>93000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-221000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-181000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-167000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-156000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-177000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-121000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-141000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-198000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>360000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-152000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-141000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-148000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-155000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-162000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-239000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-182000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-167000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-161000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>26000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-90000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-358000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-218000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-94000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-72000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>497000</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-98000</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3044000</v>
+      </c>
+      <c r="E33" s="3">
         <v>3932000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4319000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4750000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3615000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3769000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4630000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3959000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3137000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3754000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3468000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4521000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>3384000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3397000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>3863000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>3868000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2979000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>3287000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>4153000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>4042000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2832000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>3204000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>3788000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>4211000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>2730000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>2853000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>3653000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>3528000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-5309000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>2681000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>3129000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>3133000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1824000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>2437000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>2433000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>2791000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>2152000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>2462000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>7814000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>2651000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3854,257 +3929,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3044000</v>
+      </c>
+      <c r="E35" s="3">
         <v>3932000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4319000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4750000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3615000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3769000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4630000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3959000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3137000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3754000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3468000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4521000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>3384000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3397000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>3863000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>3868000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2979000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>3287000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>4153000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>4042000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2832000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>3204000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>3788000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>4211000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>2730000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>2853000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>3653000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>3528000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-5309000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>2681000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>3129000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>3133000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1824000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>2437000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>2433000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>2791000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>2152000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>2462000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>7814000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>2651000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4147,8 +4231,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4191,130 +4276,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9942000</v>
+      </c>
+      <c r="E41" s="3">
         <v>12306000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>10825000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>11171000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>9556000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>9116000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>10230000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>12156000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>9482000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6828000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7890000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>9733000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8246000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7596000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>6854000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>6710000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7214000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>8526000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>11544000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>10370000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>10288000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>10007000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>11941000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>13392000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>16181000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>15393000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>6279000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>9304000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4239000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2738000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3696000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2545000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2569000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>5326000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>7432000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>5024000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>5569000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>5817000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>6051000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>7456000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4400,287 +4489,296 @@
         <v>0</v>
       </c>
       <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF42" s="3">
         <v>6048000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>7085000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>8421000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>8708000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>9281000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>10208000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>11326000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>10983000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>9568000</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>8510000</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>7403000</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>6615000</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6056000</v>
+      </c>
+      <c r="E43" s="3">
         <v>6322000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6279000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6487000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6185000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6139000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>6234000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6314000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6118000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6124000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>6334000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6215000</v>
-      </c>
-      <c r="O43" s="3">
-        <v>5471000</v>
       </c>
       <c r="P43" s="3">
         <v>5471000</v>
       </c>
       <c r="Q43" s="3">
+        <v>5471000</v>
+      </c>
+      <c r="R43" s="3">
         <v>5767000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5720000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>5143000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>5513000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>5241000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>5662000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>4725000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>4861000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>4819000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>5043000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>4178000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>4640000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>5196000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>5143000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>4951000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>5198000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>5055000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>5035000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>4686000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>5149000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>5182000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>4942000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>4594000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>4358000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>4729000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>4713000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>8170000</v>
+      </c>
+      <c r="E44" s="3">
         <v>7853000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>7818000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>7848000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>7550000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>7400000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>7020000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>7287000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>7016000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>7078000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>7152000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>7117000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>7073000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>7483000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>7541000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>7590000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>6924000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>7101000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>6673000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>6307000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>5983000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>6002000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>5957000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>5707000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>5498000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>5330000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>5521000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>5465000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>5017000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>5358000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>5281000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>5182000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>4738000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>5207000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>5131000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>5023000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>4624000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>4754000</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>4787000</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>4999000</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4693,11 +4791,11 @@
       <c r="F45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3">
         <v>1000</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>8</v>
@@ -4723,208 +4821,214 @@
       <c r="P45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R45" s="3">
         <v>1704000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2501000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2372000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2276000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2087000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1997000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2095000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1738000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1938000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1884000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2130000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1777000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1921000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>2013000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>2218000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1933000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1978000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1876000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>2046000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>2070000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>2143000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>2124000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>2139000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>2446000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>2602000</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>11388000</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>26208000</v>
+      </c>
+      <c r="E46" s="3">
         <v>27987000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>26588000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>27118000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>25392000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>24435000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>25642000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>27449000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>24709000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>22458000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>23111000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>24940000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>22648000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>22305000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>21866000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>22521000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>21653000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>23416000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>25545000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>24336000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>23091000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>22608000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>24655000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>26026000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>27987000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>27140000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>18917000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>21925000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>22473000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>22312000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>24431000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>23346000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>23320000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>27960000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>31214000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>28096000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>26494000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>25885000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>25572000</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>35171000</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4964,23 +5068,23 @@
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P47" s="3">
+      <c r="P47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q47" s="3">
         <v>91000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>60000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>66000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>113000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>126000</v>
-      </c>
-      <c r="U47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="V47" s="3" t="s">
         <v>8</v>
@@ -4994,8 +5098,8 @@
       <c r="Y47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z47" s="3">
-        <v>0</v>
+      <c r="Z47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA47" s="3">
         <v>0</v>
@@ -5045,252 +5149,261 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>26206000</v>
+      </c>
+      <c r="E48" s="3">
         <v>24574000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>24487000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>24119000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>24822000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>22728000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>22074000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>22506000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>23027000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>22027000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>22132000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>21636000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>22690000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>21564000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>21167000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>20593000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>21195000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>21323000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>21357000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>21392000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>21686000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>21103000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>21416000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>20876000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>21542000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>21314000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>22153000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>21788000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>21271000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>20993000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>20822000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>20590000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>20600000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>20925000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>20420000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>20108000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>19893000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>19219000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>18778000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>19310000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>62720000</v>
+      </c>
+      <c r="E49" s="3">
         <v>62890000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>63402000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>63461000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>63560000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>62312000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>61731000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>63023000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>62350000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>62760000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>63218000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>63876000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>64442000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>64550000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>63545000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>62226000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>63379000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>64623000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>63853000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>63997000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>64566000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>64270000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>65245000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>64383000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>63693000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>63451000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>63978000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>63607000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>64488000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>72589000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>72879000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>69144000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>69077000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>70304000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>69848000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>69451000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>68886000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>67835000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>67643000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>68887000</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5411,8 +5524,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5533,130 +5649,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>11387000</v>
+      </c>
+      <c r="E52" s="3">
         <v>12927000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>12809000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>12901000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>11457000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>13509000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>13192000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>13504000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>12284000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>12353000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>12248000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>12079000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>11049000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>11341000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>11077000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>10876000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>10868000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>10729000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>10661000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>9944000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>9964000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>8797000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>8796000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>8614000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>7478000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>6655000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>6675000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>6738000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>6863000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>5779000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>5555000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>5360000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>5313000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>5180000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>5162000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>5196000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>5133000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>5152000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>5040000</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>5675000</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5777,130 +5899,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>126521000</v>
+      </c>
+      <c r="E54" s="3">
         <v>128378000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>127286000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>127599000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>125231000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>122984000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>122639000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>126482000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>122370000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>119598000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>120709000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>122531000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>120829000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>119851000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>117715000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>116282000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>117208000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>120217000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>121416000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>119669000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>119307000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>116778000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>120112000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>119899000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>120700000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>118560000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>111723000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>114058000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>115095000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>121673000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>123687000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>118440000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>118310000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>124369000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>126644000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>122851000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>120406000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>118091000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>117033000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>129043000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5943,8 +6071,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5987,269 +6116,276 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>16306000</v>
+      </c>
+      <c r="E57" s="3">
         <v>15030000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>15173000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>15609000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>15227000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>14512000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>14495000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>15350000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>15364000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>13691000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>14234000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>14435000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>14598000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>13790000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>14153000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>14845000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>14882000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>14175000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>14154000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>14223000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>13720000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>12134000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>12027000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>11935000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>12071000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>10464000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>10781000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>10951000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>11260000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>10207000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>10266000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>10243000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>10344000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>9716000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>9740000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>9458000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>9632000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>8076000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>8300000</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>9024000</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>11542000</v>
+      </c>
+      <c r="E58" s="3">
         <v>13174000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>11062000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>11631000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>10395000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>9889000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>9424000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>10409000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>7465000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>7729000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>10616000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>11811000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>11082000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>13717000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>14300000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>11717000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>8645000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>9902000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>13331000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>11989000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>8889000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>8773000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>8586000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>7707000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>11183000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>12701000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>9153000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>9352000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>9697000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>8911000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>12113000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>10508000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>10423000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>12862000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>15547000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>14026000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>13554000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>13781000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>13007000</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>12215000</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
+      <c r="D59" s="3">
+        <v>4361000</v>
+      </c>
+      <c r="E59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1000</v>
       </c>
-      <c r="F59" s="3" t="s">
+      <c r="G59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4286000</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>8</v>
@@ -6257,11 +6393,11 @@
       <c r="J59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L59" s="3">
         <v>4183000</v>
-      </c>
-      <c r="L59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M59" s="3" t="s">
         <v>8</v>
@@ -6269,458 +6405,470 @@
       <c r="N59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P59" s="3">
         <v>3917000</v>
       </c>
-      <c r="P59" s="3" t="s">
+      <c r="Q59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>10293000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>10056000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>9554000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>10324000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>10542000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>10377000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>10523000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>11109000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>11131000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>10366000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>9722000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>9731000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>10230000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>9950000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>9054000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>9252000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>8868000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>8469000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>7470000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>8133000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>7820000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>7240000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>7024000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>7225000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>7584000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>11162000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>38694000</v>
+      </c>
+      <c r="E60" s="3">
         <v>38235000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>36699000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>37995000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>36058000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>34248000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>33797000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>36420000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>33627000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>32340000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>35950000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>37158000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>35756000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>38030000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>38746000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>36618000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>33081000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>34401000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>38027000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>36589000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>33132000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>32016000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>31744000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>30008000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>32976000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>32896000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>30164000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>30253000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>30011000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>28370000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>31247000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>29220000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>28237000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>30711000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>33107000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>30724000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>30210000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>29082000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>28891000</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>32401000</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>23483000</v>
+      </c>
+      <c r="E61" s="3">
         <v>23852000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>25577000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>24315000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>26131000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>24252000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>25263000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>25744000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>26260000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>24253000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>23096000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>24069000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>25418000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>22874000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>20582000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>21286000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>22848000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>23767000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>22322000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>20558000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>23099000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>21053000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>22514000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>23948000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>23537000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>23310000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>18985000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>20161000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>20395000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>21359000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>21514000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>20779000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>20863000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>22437000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>22186000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>20188000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>18038000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>16633000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>16460000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>18910000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1333000</v>
+      </c>
+      <c r="E62" s="3">
         <v>5513000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>5719000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>5845000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1267000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5458000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5411000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>5758000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1872000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>6388000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>6616000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>6477000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2306000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>7104000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>13662000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>14044000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>14425000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>16303000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>16174000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>16114000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>16422000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>16790000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>17314000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>17367000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>17309000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>16413000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>16666000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>16660000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>17110000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>16392000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>16483000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>15937000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>16327000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>16275000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>16630000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>16524000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>16380000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>17828000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>17938000</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>18781000</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6841,8 +6989,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6963,8 +7114,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7085,130 +7239,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>72210000</v>
+      </c>
+      <c r="E66" s="3">
         <v>73647000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>73969000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>74048000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>72947000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>70439000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>71196000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>74342000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>71812000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>69265000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>71881000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>74518000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>73764000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>74430000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>73260000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>72207000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>70619000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>74739000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>76798000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>73558000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>72929000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>70182000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>71931000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>71717000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>74179000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>73020000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>66185000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>67480000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>67901000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>66601000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>69697000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>66204000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>66017000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>70054000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>72532000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>68033000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>65222000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>64251000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>63973000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>70781000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7251,8 +7411,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7373,8 +7534,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7495,130 +7659,136 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>756000</v>
+      </c>
+      <c r="E70" s="3">
         <v>759000</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>767000</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>770000</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>777000</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>781000</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>788000</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>791000</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>798000</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>801000</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>809000</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>812000</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>819000</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>822000</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>831000</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <v>834000</v>
       </c>
-      <c r="S70" s="3">
+      <c r="T70" s="3">
         <v>843000</v>
       </c>
-      <c r="T70" s="3">
+      <c r="U70" s="3">
         <v>846000</v>
       </c>
-      <c r="U70" s="3">
+      <c r="V70" s="3">
         <v>856000</v>
       </c>
-      <c r="V70" s="3">
+      <c r="W70" s="3">
         <v>859000</v>
       </c>
-      <c r="W70" s="3">
+      <c r="X70" s="3">
         <v>870000</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Y70" s="3">
         <v>873000</v>
       </c>
-      <c r="Y70" s="3">
+      <c r="Z70" s="3">
         <v>885000</v>
       </c>
-      <c r="Z70" s="3">
+      <c r="AA70" s="3">
         <v>888000</v>
       </c>
-      <c r="AA70" s="3">
+      <c r="AB70" s="3">
         <v>897000</v>
       </c>
-      <c r="AB70" s="3">
+      <c r="AC70" s="3">
         <v>900000</v>
       </c>
-      <c r="AC70" s="3">
+      <c r="AD70" s="3">
         <v>911000</v>
       </c>
-      <c r="AD70" s="3">
+      <c r="AE70" s="3">
         <v>915000</v>
       </c>
-      <c r="AE70" s="3">
+      <c r="AF70" s="3">
         <v>928000</v>
       </c>
-      <c r="AF70" s="3">
+      <c r="AG70" s="3">
         <v>933000</v>
       </c>
-      <c r="AG70" s="3">
+      <c r="AH70" s="3">
         <v>946000</v>
       </c>
-      <c r="AH70" s="3">
+      <c r="AI70" s="3">
         <v>951000</v>
       </c>
-      <c r="AI70" s="3">
+      <c r="AJ70" s="3">
         <v>967000</v>
       </c>
-      <c r="AJ70" s="3">
+      <c r="AK70" s="3">
         <v>972000</v>
       </c>
-      <c r="AK70" s="3">
+      <c r="AL70" s="3">
         <v>986000</v>
       </c>
-      <c r="AL70" s="3">
+      <c r="AM70" s="3">
         <v>991000</v>
       </c>
-      <c r="AM70" s="3">
+      <c r="AN70" s="3">
         <v>1006000</v>
       </c>
-      <c r="AN70" s="3">
+      <c r="AO70" s="3">
         <v>1010000</v>
       </c>
-      <c r="AO70" s="3">
+      <c r="AP70" s="3">
         <v>1024000</v>
       </c>
-      <c r="AP70" s="3">
+      <c r="AQ70" s="3">
         <v>1029000</v>
       </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7739,130 +7909,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>135852000</v>
+      </c>
+      <c r="E72" s="3">
         <v>135424000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>133981000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>132212000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>129973000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>128919000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>127544000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>125361000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>123811000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>123132000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>121617000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>120443000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>118170000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>117082000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>115858000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>114163000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>112429000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>111645000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>110393000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>108361000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>106374000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>105674000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>104361000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>102539000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>100239000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>99474000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>98414000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>96625000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>94918000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>102103000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>101170000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>99831000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>98641000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>98623000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>97881000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>97197000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>96124000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>95736000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>94945000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>88855000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7983,8 +8159,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8105,8 +8284,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8227,130 +8409,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>53325000</v>
+      </c>
+      <c r="E76" s="3">
         <v>53746000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>52274000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>52500000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>51235000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>51491000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>50380000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>51049000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>49488000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>49257000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>47725000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>46880000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>45958000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>44318000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>43624000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>43241000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>45746000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>44632000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>43762000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>45252000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>45508000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>45723000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>47296000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>47294000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>45624000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>44640000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>44627000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>45663000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>46266000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>54139000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>53044000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>51285000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>51326000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>53343000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>53126000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>53827000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>54178000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>52830000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>52036000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>57233000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8471,257 +8659,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3044000</v>
+      </c>
+      <c r="E81" s="3">
         <v>3932000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4319000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4750000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3615000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3769000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4630000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3959000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3137000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3754000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3468000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4521000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>3384000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3397000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>3863000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>3868000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2979000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>3287000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>4153000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>4042000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2832000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>3204000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>3788000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>4211000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>2730000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>2853000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>3653000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>3528000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-5309000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>2681000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>3129000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>3133000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1824000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>2437000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>2433000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>2791000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>2152000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>2462000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>7814000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>2651000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8764,130 +8961,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>644000</v>
+      </c>
+      <c r="E83" s="3">
         <v>612000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>626000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>645000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>678000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>628000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>637000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>615000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>620000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>610000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>574000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>583000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>640000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>611000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>653000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>663000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>722000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>690000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>684000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>711000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>710000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>683000</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>671000</v>
       </c>
       <c r="Z83" s="3">
         <v>671000</v>
       </c>
       <c r="AA83" s="3">
+        <v>671000</v>
+      </c>
+      <c r="AB83" s="3">
         <v>814000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>799000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>677000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>723000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>820000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>711000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>650000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>643000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>750000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>716000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>676000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>692000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>720000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>665000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>707000</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>728000</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9008,8 +9209,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9130,8 +9334,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9252,8 +9459,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9374,8 +9584,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9496,130 +9709,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>5131000</v>
+      </c>
+      <c r="E89" s="3">
         <v>4045000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4972000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>5408000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>4985000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3705000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>4825000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>4302000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>5754000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>4088000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>5100000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>4904000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>5341000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3863000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3574000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>4070000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>3713000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>3246000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>5121000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>4643000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>4121000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>4087000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>5424000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>4739000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>4806000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>4064000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>4364000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>4169000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>4151000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>3517000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>4007000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>3567000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>4199000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>3353000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>3684000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>3631000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>3688000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>3040000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>3000000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>3025000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9662,130 +9881,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1023000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1019000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1167000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1200000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-996000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-859000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-925000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-993000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-783000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-797000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-817000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-925000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-734000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-730000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-708000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-890000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-692000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-747000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-626000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1091000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-714000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-656000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-567000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-850000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-658000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-731000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-605000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1079000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-814000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-752000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-701000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-1080000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-907000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-910000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-768000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-1132000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-1154000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-801000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-745000</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-684000</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9906,8 +10129,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10028,130 +10254,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1196000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-665000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1228000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1535000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1063000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-726000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-921000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1108000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-518000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-762000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1002000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1222000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-798000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1380000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-490000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-832000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-682000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1776000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-960000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1006000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-791000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-665000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-549000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-829000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-659000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-725000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-650000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>5079000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>647000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>573000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-3845000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-865000</v>
-      </c>
-      <c r="AI94" s="3">
-        <v>97000</v>
       </c>
       <c r="AJ94" s="3">
         <v>97000</v>
       </c>
       <c r="AK94" s="3">
+        <v>97000</v>
+      </c>
+      <c r="AL94" s="3">
         <v>-1171000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-2534000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-1866000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-1802000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>100000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-2121000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10194,8 +10426,9 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10238,86 +10471,89 @@
       <c r="P96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="Q96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R96" s="3">
         <v>566000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-2184000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-2171000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-2035000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-2171000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-2112000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-2197000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-2143000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-1959000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-1964000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-2028000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-2035000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-1859000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-1867000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-1937000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-1858000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-1850000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-1853000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-1861000</v>
-      </c>
-      <c r="AJ96" s="3">
-        <v>-1813000</v>
       </c>
       <c r="AK96" s="3">
         <v>-1813000</v>
       </c>
       <c r="AL96" s="3">
+        <v>-1813000</v>
+      </c>
+      <c r="AM96" s="3">
         <v>-1823000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-1826000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-1773000</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-1786000</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-1851000</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10438,8 +10674,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10560,8 +10799,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10682,370 +10924,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-6306000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1827000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4088000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2239000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3616000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-4215000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-5571000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-634000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2499000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-4269000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-6049000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2038000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-3893000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1753000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2993000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-3507000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-4158000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-4432000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-2858000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-3428000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-3085000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-5275000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-6441000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-6730000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-3399000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>5945000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-6795000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-4118000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-3304000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-5066000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>1032000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-2656000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-6861000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-5638000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-152000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-1724000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-2229000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-1600000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-4232000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-507000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>134000</v>
+      </c>
+      <c r="E101" s="3">
         <v>122000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-260000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>116000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-83000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-119000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>107000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-156000</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
       <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>12000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>53000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-235000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-185000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-56000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>53000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-235000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-185000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-56000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-129000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-127000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>36000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-81000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>115000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>31000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>40000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-170000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>56000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-65000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>7000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>18000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-43000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-70000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-192000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>82000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>47000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>82000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>159000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>128000</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-273000</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-43000</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2363000</v>
+      </c>
+      <c r="E102" s="3">
         <v>1480000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-345000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1614000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>440000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1114000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1927000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2676000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2654000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1062000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1844000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1488000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>650000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>742000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>144000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-504000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1312000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-3018000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1174000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>82000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>281000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1934000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1451000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-2789000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>788000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>9114000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-3025000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>5065000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1501000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-958000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>1151000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-24000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-2757000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-2106000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>2408000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-545000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-248000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-234000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-1405000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>354000</v>
       </c>
     </row>
